--- a/data/Aim2.1_CFU_statistics_summary.xlsx
+++ b/data/Aim2.1_CFU_statistics_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/af327/Desktop/R/encapsulation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A6AE64-B821-AD48-A456-083CF27A567C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E86415F-6615-D14C-BAFC-03E1300AD877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22860" yWindow="-1460" windowWidth="22700" windowHeight="19900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="760" windowWidth="22700" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total_Means_SE" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,23 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Component_Tukey!$A$1:$A$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Total_Means_SE!$C$1:$C$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Total_Tukey!$A$1:$A$61</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -856,6 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -879,7 +894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -939,7 +954,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -999,7 +1014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1059,7 +1074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1119,7 +1134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1179,7 +1194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1239,7 +1254,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1299,7 +1314,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -1359,7 +1374,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>7</v>
       </c>
@@ -1410,7 +1425,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>14</v>
       </c>
@@ -1462,6 +1477,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C31" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="21"/>
+        <filter val="42"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
